--- a/data/progbook_inputs_coverage_20.xlsx
+++ b/data/progbook_inputs_coverage_20.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://burnetinstitute.sharepoint.com/sites/WG-Modelling-HCVvaccinemodel/Shared Documents/HCV vaccine model/HCV vaccine model/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{5260720A-E352-4F90-B81D-5AD4DCF21178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D82A3DA-B9D7-4AF6-82C3-578330080B66}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEA833B-8BFF-4EDE-B15F-9F4C13B7D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
   </bookViews>
   <sheets>
     <sheet name="interventions" sheetId="7" r:id="rId1"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="87">
   <si>
     <t>code</t>
   </si>
@@ -737,6 +737,12 @@
   </si>
   <si>
     <t>PWID + Campaign + Prison + Schools + Adults</t>
+  </si>
+  <si>
+    <t>Prisoners_PWID_males</t>
+  </si>
+  <si>
+    <t>Prisoners_PWID_females</t>
   </si>
 </sst>
 </file>
@@ -987,7 +993,17 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1325,13 +1341,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7293DEF-C325-4FE3-AD5B-B41F22CF0DA3}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1339,7 +1355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>38</v>
       </c>
@@ -1347,7 +1363,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
@@ -1355,7 +1371,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1363,7 +1379,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -1371,7 +1387,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>41</v>
       </c>
@@ -1379,7 +1395,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>64</v>
       </c>
@@ -1387,7 +1403,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>65</v>
       </c>
@@ -1395,7 +1411,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1403,70 +1419,70 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="3"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="3"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="3"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="3"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="3"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="3"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="3"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="3"/>
     </row>
   </sheetData>
@@ -1477,25 +1493,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B95C70-A891-4037-BF3D-C1EB7C57DA84}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O47"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1535,8 +1551,14 @@
       <c r="M1" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -1558,7 +1580,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -1580,7 +1602,7 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -1601,8 +1623,14 @@
       <c r="M4" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -1623,8 +1651,10 @@
       <c r="K5" s="11"/>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="11"/>
+      <c r="O5" s="11"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -1645,8 +1675,10 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
       <c r="M6" s="11"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -1667,8 +1699,10 @@
       <c r="K7" s="11"/>
       <c r="L7" s="11"/>
       <c r="M7" s="11"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -1689,8 +1723,14 @@
       <c r="M8" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
@@ -1731,8 +1771,14 @@
       <c r="M9" s="11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
@@ -1750,7 +1796,7 @@
       <c r="L10" s="11"/>
       <c r="M10" s="11"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
@@ -1768,7 +1814,7 @@
       <c r="L11" s="11"/>
       <c r="M11" s="11"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
@@ -1786,7 +1832,7 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
@@ -1804,7 +1850,7 @@
       <c r="L13" s="11"/>
       <c r="M13" s="11"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
@@ -1822,7 +1868,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
@@ -1840,7 +1886,7 @@
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
@@ -1858,7 +1904,7 @@
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
@@ -1876,7 +1922,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
@@ -1894,7 +1940,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
@@ -1912,7 +1958,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
@@ -1930,7 +1976,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
@@ -1948,7 +1994,7 @@
       <c r="L21" s="11"/>
       <c r="M21" s="11"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
@@ -1966,7 +2012,7 @@
       <c r="L22" s="11"/>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
@@ -1984,7 +2030,7 @@
       <c r="L23" s="11"/>
       <c r="M23" s="11"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
@@ -2002,7 +2048,7 @@
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
@@ -2020,7 +2066,7 @@
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
@@ -2038,7 +2084,7 @@
       <c r="L26" s="11"/>
       <c r="M26" s="11"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
@@ -2056,7 +2102,7 @@
       <c r="L27" s="11"/>
       <c r="M27" s="11"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
@@ -2074,7 +2120,7 @@
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
@@ -2092,7 +2138,7 @@
       <c r="L29" s="11"/>
       <c r="M29" s="11"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
@@ -2110,7 +2156,7 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
@@ -2128,7 +2174,7 @@
       <c r="L31" s="11"/>
       <c r="M31" s="11"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
@@ -2146,7 +2192,7 @@
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
@@ -2164,7 +2210,7 @@
       <c r="L33" s="11"/>
       <c r="M33" s="11"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
@@ -2182,7 +2228,7 @@
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
@@ -2200,7 +2246,7 @@
       <c r="L35" s="11"/>
       <c r="M35" s="11"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
@@ -2218,7 +2264,7 @@
       <c r="L36" s="11"/>
       <c r="M36" s="11"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
@@ -2236,7 +2282,7 @@
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
@@ -2254,7 +2300,7 @@
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
@@ -2272,7 +2318,7 @@
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
@@ -2290,7 +2336,7 @@
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
@@ -2308,7 +2354,7 @@
       <c r="L41" s="11"/>
       <c r="M41" s="11"/>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
@@ -2326,7 +2372,7 @@
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
@@ -2344,7 +2390,7 @@
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
@@ -2362,7 +2408,7 @@
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
@@ -2380,7 +2426,7 @@
       <c r="L45" s="11"/>
       <c r="M45" s="11"/>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
@@ -2398,7 +2444,7 @@
       <c r="L46" s="11"/>
       <c r="M46" s="11"/>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -2418,7 +2464,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:M47">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"y"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:O9">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2430,20 +2481,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDB1B9B-545D-4297-BB39-C50701A07DD3}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2473,7 +2524,7 @@
       </c>
       <c r="K1" s="8"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -2485,7 +2536,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -2506,7 +2557,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -2527,7 +2578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -2539,7 +2590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -2551,7 +2602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -2572,7 +2623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -2593,7 +2644,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
@@ -2623,231 +2674,231 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
       </c>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
       </c>
       <c r="D36" s="6"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -2855,7 +2906,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:I31">
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2868,20 +2919,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193E247F-181A-4B6D-B2CD-717659CE10EB}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:J47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2913,7 +2964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -2934,7 +2985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -2955,7 +3006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -2977,7 +3028,7 @@
       </c>
       <c r="J4" s="9"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -2998,7 +3049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -3019,7 +3070,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -3040,7 +3091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -3061,7 +3112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
@@ -3082,7 +3133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
@@ -3092,7 +3143,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
@@ -3102,7 +3153,7 @@
       <c r="D11" s="2"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
@@ -3112,7 +3163,7 @@
       <c r="D12" s="2"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
@@ -3122,7 +3173,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
@@ -3132,7 +3183,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
@@ -3142,7 +3193,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
@@ -3152,7 +3203,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
@@ -3162,7 +3213,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
@@ -3172,7 +3223,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="1"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
@@ -3182,7 +3233,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
@@ -3192,7 +3243,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="1"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
@@ -3202,7 +3253,7 @@
       <c r="D21" s="2"/>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
@@ -3212,7 +3263,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="1"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
@@ -3222,7 +3273,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
@@ -3232,7 +3283,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
@@ -3242,7 +3293,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
@@ -3252,7 +3303,7 @@
       <c r="D26" s="2"/>
       <c r="E26" s="1"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
@@ -3262,7 +3313,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
@@ -3272,7 +3323,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
@@ -3282,7 +3333,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
@@ -3292,7 +3343,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="1"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
@@ -3302,7 +3353,7 @@
       <c r="D31" s="2"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
@@ -3311,7 +3362,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
@@ -3320,7 +3371,7 @@
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
@@ -3329,7 +3380,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
@@ -3338,7 +3389,7 @@
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
@@ -3347,7 +3398,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
@@ -3356,7 +3407,7 @@
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
@@ -3365,7 +3416,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
@@ -3374,7 +3425,7 @@
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
@@ -3383,7 +3434,7 @@
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
@@ -3392,7 +3443,7 @@
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
@@ -3401,7 +3452,7 @@
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
@@ -3410,7 +3461,7 @@
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
@@ -3419,7 +3470,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
@@ -3428,7 +3479,7 @@
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
@@ -3437,7 +3488,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -3461,26 +3512,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B5232EA-A822-4ED1-B8AA-05F696E2FA18}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:O47"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.7265625" customWidth="1"/>
+    <col min="11" max="11" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3523,7 +3574,7 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="str">
         <f>IF(ISBLANK(interventions!A2),"",interventions!A2)</f>
         <v>pwid_vax</v>
@@ -3535,7 +3586,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="str">
         <f>IF(ISBLANK(interventions!A3),"",interventions!A3)</f>
         <v>pwid_vax_campaign</v>
@@ -3565,7 +3616,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="str">
         <f>IF(ISBLANK(interventions!A4),"",interventions!A4)</f>
         <v>prison_vax_campaign</v>
@@ -3595,7 +3646,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="str">
         <f>IF(ISBLANK(interventions!A5),"",interventions!A5)</f>
         <v>teen_vax</v>
@@ -3607,7 +3658,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="str">
         <f>IF(ISBLANK(interventions!A6),"",interventions!A6)</f>
         <v>adults_vax</v>
@@ -3619,7 +3670,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="str">
         <f>IF(ISBLANK(interventions!A7),"",interventions!A7)</f>
         <v>pwid_counter</v>
@@ -3643,7 +3694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="str">
         <f>IF(ISBLANK(interventions!A8),"",interventions!A8)</f>
         <v>prison_counter</v>
@@ -3667,241 +3718,241 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="str">
         <f>IF(ISBLANK(interventions!A9),"",interventions!A9)</f>
         <v>status_quo</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="str">
         <f>IF(ISBLANK(interventions!A10),"",interventions!A10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="str">
         <f>IF(ISBLANK(interventions!A11),"",interventions!A11)</f>
         <v/>
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="str">
         <f>IF(ISBLANK(interventions!A12),"",interventions!A12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="str">
         <f>IF(ISBLANK(interventions!A13),"",interventions!A13)</f>
         <v/>
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="str">
         <f>IF(ISBLANK(interventions!A14),"",interventions!A14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="str">
         <f>IF(ISBLANK(interventions!A15),"",interventions!A15)</f>
         <v/>
       </c>
       <c r="H15" s="5"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="str">
         <f>IF(ISBLANK(interventions!A16),"",interventions!A16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="str">
         <f>IF(ISBLANK(interventions!A17),"",interventions!A17)</f>
         <v/>
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="str">
         <f>IF(ISBLANK(interventions!A18),"",interventions!A18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="str">
         <f>IF(ISBLANK(interventions!A19),"",interventions!A19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="str">
         <f>IF(ISBLANK(interventions!A20),"",interventions!A20)</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="str">
         <f>IF(ISBLANK(interventions!A21),"",interventions!A21)</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="str">
         <f>IF(ISBLANK(interventions!A22),"",interventions!A22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="str">
         <f>IF(ISBLANK(interventions!A23),"",interventions!A23)</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="str">
         <f>IF(ISBLANK(interventions!A24),"",interventions!A24)</f>
         <v/>
       </c>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="str">
         <f>IF(ISBLANK(interventions!A25),"",interventions!A25)</f>
         <v/>
       </c>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="str">
         <f>IF(ISBLANK(interventions!A26),"",interventions!A26)</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="str">
         <f>IF(ISBLANK(interventions!A27),"",interventions!A27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="str">
         <f>IF(ISBLANK(interventions!A28),"",interventions!A28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="str">
         <f>IF(ISBLANK(interventions!A29),"",interventions!A29)</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="str">
         <f>IF(ISBLANK(interventions!A30),"",interventions!A30)</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="str">
         <f>IF(ISBLANK(interventions!A31),"",interventions!A31)</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="str">
         <f>IF(ISBLANK(interventions!A32),"",interventions!A32)</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="str">
         <f>IF(ISBLANK(interventions!A33),"",interventions!A33)</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="str">
         <f>IF(ISBLANK(interventions!A34),"",interventions!A34)</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="str">
         <f>IF(ISBLANK(interventions!A35),"",interventions!A35)</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="str">
         <f>IF(ISBLANK(interventions!A36),"",interventions!A36)</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="4" t="str">
         <f>IF(ISBLANK(interventions!A37),"",interventions!A37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="str">
         <f>IF(ISBLANK(interventions!A38),"",interventions!A38)</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="str">
         <f>IF(ISBLANK(interventions!A39),"",interventions!A39)</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="str">
         <f>IF(ISBLANK(interventions!A40),"",interventions!A40)</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="str">
         <f>IF(ISBLANK(interventions!A41),"",interventions!A41)</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="str">
         <f>IF(ISBLANK(interventions!A42),"",interventions!A42)</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="str">
         <f>IF(ISBLANK(interventions!A43),"",interventions!A43)</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="str">
         <f>IF(ISBLANK(interventions!A44),"",interventions!A44)</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="str">
         <f>IF(ISBLANK(interventions!A45),"",interventions!A45)</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="str">
         <f>IF(ISBLANK(interventions!A46),"",interventions!A46)</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="str">
         <f>IF(ISBLANK(interventions!A47),"",interventions!A47)</f>
         <v/>
@@ -3922,17 +3973,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C010CA95-9913-4E01-BBC8-E12EAEB492A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="27" t="s">
         <v>55</v>
       </c>
@@ -3952,7 +4003,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
         <v>71</v>
       </c>
@@ -3969,7 +4020,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>72</v>
       </c>
@@ -3987,7 +4038,7 @@
       </c>
       <c r="F3" s="31"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
         <v>73</v>
       </c>
@@ -4005,7 +4056,7 @@
       </c>
       <c r="F4" s="29"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="26" t="s">
         <v>73</v>
       </c>
@@ -4023,7 +4074,7 @@
       </c>
       <c r="F5" s="21"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>74</v>
       </c>
@@ -4043,7 +4094,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="16" t="s">
         <v>75</v>
       </c>
@@ -4063,7 +4114,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="24" t="s">
         <v>75</v>
       </c>
@@ -4081,7 +4132,7 @@
       </c>
       <c r="F8" s="21"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>76</v>
       </c>
@@ -4101,7 +4152,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>76</v>
       </c>
@@ -4118,7 +4169,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="23" t="s">
         <v>76</v>
       </c>
@@ -4136,7 +4187,7 @@
       </c>
       <c r="F11" s="21"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="18" t="s">
         <v>77</v>
       </c>
@@ -4156,7 +4207,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="18" t="s">
         <v>77</v>
       </c>
@@ -4173,7 +4224,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="18" t="s">
         <v>77</v>
       </c>
@@ -4190,7 +4241,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
         <v>77</v>
       </c>
@@ -4208,7 +4259,7 @@
       </c>
       <c r="F15" s="21"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>78</v>
       </c>
@@ -4228,7 +4279,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="19" t="s">
         <v>78</v>
       </c>
@@ -4245,7 +4296,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
         <v>78</v>
       </c>
@@ -4262,7 +4313,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="19" t="s">
         <v>78</v>
       </c>
@@ -4279,7 +4330,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
         <v>78</v>
       </c>
@@ -4306,6 +4357,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
     <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
@@ -4477,15 +4537,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -4497,6 +4548,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090DCA50-A1C8-4B02-A520-4AE25ED4C282}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4510,14 +4569,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/data/progbook_inputs_coverage_20.xlsx
+++ b/data/progbook_inputs_coverage_20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AEA833B-8BFF-4EDE-B15F-9F4C13B7D9F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF28C24A-9589-4591-A70F-A46928DDD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
   </bookViews>
   <sheets>
     <sheet name="interventions" sheetId="7" r:id="rId1"/>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="87">
   <si>
     <t>code</t>
   </si>
@@ -1509,6 +1509,8 @@
     <col min="11" max="11" width="13.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.7265625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -1617,12 +1619,8 @@
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
       <c r="N4" s="11" t="s">
         <v>15</v>
       </c>
@@ -1717,12 +1715,8 @@
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
-      <c r="L8" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>15</v>
-      </c>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
       <c r="N8" s="11" t="s">
         <v>15</v>
       </c>
@@ -2469,7 +2463,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N4:O9">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2906,7 +2900,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:I31">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4366,6 +4360,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
     <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
@@ -4537,16 +4541,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
   <ds:schemaRefs>
@@ -4556,6 +4550,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090DCA50-A1C8-4B02-A520-4AE25ED4C282}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4571,20 +4581,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D8656-6848-4E43-8697-69A82BA725E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/progbook_inputs_coverage_20.xlsx
+++ b/data/progbook_inputs_coverage_20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farah.houdroge\Documents\GitHub\hcv-vaccine\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF28C24A-9589-4591-A70F-A46928DDD0E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD1F5E1-40A6-4C98-A3CE-CBF1F3B6A689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E2E90E70-2F54-4097-8786-78C8F6F97317}"/>
   </bookViews>
@@ -482,7 +482,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="87">
   <si>
     <t>code</t>
   </si>
@@ -1619,8 +1619,12 @@
       <c r="I4" s="11"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
+      <c r="L4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="N4" s="11" t="s">
         <v>15</v>
       </c>
@@ -1715,8 +1719,12 @@
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
+      <c r="L8" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>15</v>
+      </c>
       <c r="N8" s="11" t="s">
         <v>15</v>
       </c>
@@ -2457,12 +2465,12 @@
       <c r="M47" s="11"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:M47">
+  <conditionalFormatting sqref="B2:M3 B9:M47 B4:K8">
     <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"y"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:O9">
+  <conditionalFormatting sqref="N4:O9 L4:M8">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"y"</formula>
     </cfRule>
@@ -4351,25 +4359,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010042DC9346A4EFF44B9278E035670E998A" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b6002ac4d6852791cc52372fb08f1f93">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="460e4ad2-c64b-4f67-8552-094351f252e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d81800e77b8320248f69566da91fdce8" ns2:_="">
     <xsd:import namespace="460e4ad2-c64b-4f67-8552-094351f252e3"/>
@@ -4541,10 +4530,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="460e4ad2-c64b-4f67-8552-094351f252e3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090DCA50-A1C8-4B02-A520-4AE25ED4C282}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4566,19 +4584,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090DCA50-A1C8-4B02-A520-4AE25ED4C282}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3882B21-9C06-4A25-BA73-35DB35426A28}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="460e4ad2-c64b-4f67-8552-094351f252e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>